--- a/data/trans_camb/P29A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 13,64</t>
+          <t>-3,74; 12,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,34</t>
+          <t>-0,84; 16,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 15,99</t>
+          <t>-4,63; 14,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 14,68</t>
+          <t>-2,64; 14,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 15,9</t>
+          <t>-1,37; 15,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 10,33</t>
+          <t>-3,37; 10,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 12,21</t>
+          <t>-0,7; 11,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 13,94</t>
+          <t>1,7; 13,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 11,42</t>
+          <t>-0,33; 11,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 29,52</t>
+          <t>-6,67; 26,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 39,14</t>
+          <t>-1,28; 35,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 34,6</t>
+          <t>-8,07; 31,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 60,59</t>
+          <t>-8,44; 61,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 66,41</t>
+          <t>-4,57; 63,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 45,92</t>
+          <t>-10,39; 47,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 33,96</t>
+          <t>-1,74; 31,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 38,4</t>
+          <t>3,96; 38,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 31,34</t>
+          <t>-0,8; 33,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 21,15</t>
+          <t>7,56; 20,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 16,32</t>
+          <t>3,14; 15,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 14,6</t>
+          <t>0,16; 14,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 16,77</t>
+          <t>7,52; 16,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,68</t>
+          <t>1,75; 10,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,92</t>
+          <t>6,85; 15,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,61</t>
+          <t>9,0; 17,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,66</t>
+          <t>3,07; 11,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 14,36</t>
+          <t>4,99; 14,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 54,0</t>
+          <t>16,59; 52,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 42,38</t>
+          <t>6,52; 38,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 37,42</t>
+          <t>0,71; 38,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,49; 181,14</t>
+          <t>55,65; 179,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 111,8</t>
+          <t>10,58; 109,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,97; 166,38</t>
+          <t>48,8; 165,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,4; 70,3</t>
+          <t>30,43; 70,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 48,08</t>
+          <t>10,07; 46,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 57,21</t>
+          <t>17,24; 59,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 6,26</t>
+          <t>-9,59; 6,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 10,51</t>
+          <t>-4,44; 10,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 7,09</t>
+          <t>-8,39; 6,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 14,79</t>
+          <t>0,64; 14,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 16,81</t>
+          <t>3,35; 17,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 7,22</t>
+          <t>-6,19; 6,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 8,79</t>
+          <t>-2,89; 8,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 11,52</t>
+          <t>0,55; 11,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,96</t>
+          <t>-5,6; 4,85</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 11,52</t>
+          <t>-15,06; 11,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 19,23</t>
+          <t>-7,1; 18,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 12,82</t>
+          <t>-13,15; 12,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 70,27</t>
+          <t>2,04; 68,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 80,81</t>
+          <t>11,36; 78,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 33,32</t>
+          <t>-20,97; 29,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 22,55</t>
+          <t>-6,65; 22,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 29,35</t>
+          <t>1,21; 28,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 12,73</t>
+          <t>-12,56; 12,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,39; -10,51</t>
+          <t>-24,9; -10,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 1,59</t>
+          <t>-12,63; 1,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 1,04</t>
+          <t>-16,1; 0,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,21; -9,58</t>
+          <t>-22,44; -9,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 8,58</t>
+          <t>-5,89; 8,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 0,03</t>
+          <t>-20,62; -0,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,04; -11,73</t>
+          <t>-22,02; -11,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 3,22</t>
+          <t>-7,02; 2,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -3,96</t>
+          <t>-22,35; -4,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -17,29</t>
+          <t>-36,7; -17,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 2,43</t>
+          <t>-18,53; 2,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 1,57</t>
+          <t>-23,6; 0,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,12; -29,87</t>
+          <t>-58,12; -29,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 28,72</t>
+          <t>-15,88; 28,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,6; -0,04</t>
+          <t>-55,03; -0,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,65; -25,02</t>
+          <t>-42,45; -24,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 6,94</t>
+          <t>-13,81; 6,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,09; -8,48</t>
+          <t>-44,14; -8,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 24,89</t>
+          <t>4,72; 23,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 7,57</t>
+          <t>-11,29; 8,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,58; -16,5</t>
+          <t>-33,98; -16,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 11,22</t>
+          <t>-5,16; 11,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 6,58</t>
+          <t>-8,82; 6,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -8,69</t>
+          <t>-20,09; -8,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 15,59</t>
+          <t>2,48; 15,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,85</t>
+          <t>-7,07; 5,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-25,49; -15,06</t>
+          <t>-24,88; -14,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,23; 65,54</t>
+          <t>9,88; 61,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 20,76</t>
+          <t>-23,42; 21,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,97; -41,83</t>
+          <t>-71,32; -44,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 83,33</t>
+          <t>-23,02; 79,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 47,42</t>
+          <t>-39,06; 46,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,77; -57,42</t>
+          <t>-88,08; -58,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,19; 58,76</t>
+          <t>7,31; 60,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 18,49</t>
+          <t>-21,71; 20,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,32; -55,37</t>
+          <t>-74,5; -53,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 2,63</t>
+          <t>-13,27; 2,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 8,09</t>
+          <t>-7,84; 7,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -1,2</t>
+          <t>-17,33; -1,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -0,69</t>
+          <t>-17,22; -1,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,68</t>
+          <t>-9,81; 6,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,44</t>
+          <t>-9,0; 6,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -1,87</t>
+          <t>-14,1; -1,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,22</t>
+          <t>-7,08; 4,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 0,83</t>
+          <t>-10,77; 0,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 3,93</t>
+          <t>-17,69; 3,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 12,03</t>
+          <t>-10,69; 11,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -1,94</t>
+          <t>-23,24; -2,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,43; -1,91</t>
+          <t>-39,85; -3,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 19,41</t>
+          <t>-22,85; 19,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 19,23</t>
+          <t>-20,72; 19,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -3,41</t>
+          <t>-23,86; -3,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 10,16</t>
+          <t>-12,36; 9,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 1,55</t>
+          <t>-18,72; 0,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,13; 17,78</t>
+          <t>5,75; 17,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,55; 18,21</t>
+          <t>6,86; 18,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 10,48</t>
+          <t>-1,86; 11,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 12,76</t>
+          <t>2,87; 12,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,67; 21,86</t>
+          <t>11,38; 21,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,62; 54,42</t>
+          <t>9,14; 53,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,55; 13,34</t>
+          <t>5,21; 13,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,6; 18,56</t>
+          <t>10,79; 18,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,34; 36,11</t>
+          <t>6,58; 35,36</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,77; 42,08</t>
+          <t>12,26; 42,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,36; 43,22</t>
+          <t>14,61; 43,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 24,51</t>
+          <t>-4,34; 25,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,87; 74,29</t>
+          <t>12,86; 70,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>52,32; 125,86</t>
+          <t>50,97; 122,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,97; 328,77</t>
+          <t>45,29; 301,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,39; 44,74</t>
+          <t>15,19; 43,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31,06; 61,5</t>
+          <t>31,6; 63,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19,33; 118,98</t>
+          <t>19,87; 112,27</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -3,61</t>
+          <t>-13,56; -3,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -2,01</t>
+          <t>-12,08; -2,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-51,84; -20,93</t>
+          <t>-48,89; -20,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 0,02</t>
+          <t>-9,02; -0,08</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 7,57</t>
+          <t>-1,75; 7,62</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-16,74; -9,18</t>
+          <t>-17,05; -9,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -3,02</t>
+          <t>-10,59; -3,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,82</t>
+          <t>-5,64; 1,45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -16,9</t>
+          <t>-31,84; -16,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,17; -5,99</t>
+          <t>-20,89; -5,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -3,36</t>
+          <t>-18,2; -3,59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-80,44; -33,44</t>
+          <t>-78,29; -33,09</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 0,28</t>
+          <t>-30,22; -0,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 30,83</t>
+          <t>-5,7; 31,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-56,95; -36,6</t>
+          <t>-57,84; -36,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-22,12; -6,99</t>
+          <t>-22,66; -7,74</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 4,35</t>
+          <t>-12,31; 3,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-69,18; -38,24</t>
+          <t>-71,13; -37,38</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,64</t>
+          <t>-1,45; 3,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,36</t>
+          <t>-0,47; 4,6</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -4,75</t>
+          <t>-20,69; -4,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,27</t>
+          <t>-0,99; 3,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,28</t>
+          <t>4,07; 8,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,42</t>
+          <t>-1,57; 16,54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,7</t>
+          <t>-0,72; 2,77</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,8</t>
+          <t>2,34; 5,71</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,74</t>
+          <t>-6,39; 3,24</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 6,76</t>
+          <t>-2,6; 6,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,11</t>
+          <t>-0,84; 8,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -8,72</t>
+          <t>-37,37; -8,77</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 13,86</t>
+          <t>-3,95; 13,41</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>15,98; 35,07</t>
+          <t>16,05; 35,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 67,86</t>
+          <t>-6,29; 66,32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,94</t>
+          <t>-1,81; 7,22</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,1</t>
+          <t>5,77; 14,83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 9,37</t>
+          <t>-16,09; 8,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P29A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 12,67</t>
+          <t>-3,56; 13,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 16,58</t>
+          <t>0,32; 16,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 14,7</t>
+          <t>-5,94; 10,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 14,18</t>
+          <t>-1,64; 14,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 15,08</t>
+          <t>-0,96; 14,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 10,97</t>
+          <t>-4,13; 9,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 11,65</t>
+          <t>-0,84; 12,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,95</t>
+          <t>1,43; 14,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,98</t>
+          <t>-3,83; 8,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 26,6</t>
+          <t>-6,42; 29,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 35,67</t>
+          <t>0,8; 36,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 31,14</t>
+          <t>-10,83; 22,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 61,15</t>
+          <t>-5,47; 59,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 63,38</t>
+          <t>-3,14; 61,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 47,53</t>
+          <t>-12,76; 42,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 31,33</t>
+          <t>-2,06; 32,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 38,13</t>
+          <t>3,26; 38,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 33,41</t>
+          <t>-8,95; 22,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,35</t>
+          <t>8,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 20,64</t>
+          <t>8,05; 21,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 15,27</t>
+          <t>2,93; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 14,75</t>
+          <t>-0,79; 13,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,92</t>
+          <t>7,58; 17,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,82</t>
+          <t>1,83; 10,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,59</t>
+          <t>6,42; 15,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,7</t>
+          <t>9,1; 17,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,82</t>
+          <t>3,6; 11,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,31</t>
+          <t>4,13; 13,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 52,36</t>
+          <t>17,51; 56,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 38,64</t>
+          <t>6,68; 41,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 38,45</t>
+          <t>-1,94; 34,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 179,22</t>
+          <t>52,42; 175,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 109,76</t>
+          <t>12,46; 107,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,8; 165,07</t>
+          <t>45,34; 163,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,43; 70,14</t>
+          <t>31,01; 71,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 46,57</t>
+          <t>12,5; 48,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 59,44</t>
+          <t>14,55; 53,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 6,65</t>
+          <t>-10,94; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 10,19</t>
+          <t>-5,67; 10,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 6,91</t>
+          <t>-7,37; 8,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 14,72</t>
+          <t>0,5; 14,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 17,22</t>
+          <t>2,57; 17,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 6,52</t>
+          <t>-6,27; 5,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 8,6</t>
+          <t>-2,47; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 11,16</t>
+          <t>0,3; 11,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,85</t>
+          <t>-5,58; 4,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,25%</t>
+          <t>-0,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-0,6%</t>
+          <t>-1,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 11,85</t>
+          <t>-17,11; 10,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 18,61</t>
+          <t>-8,82; 19,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 12,59</t>
+          <t>-11,53; 14,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 68,4</t>
+          <t>1,18; 69,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,36; 78,84</t>
+          <t>7,99; 81,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 29,09</t>
+          <t>-22,65; 28,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 22,24</t>
+          <t>-5,38; 22,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 28,68</t>
+          <t>0,69; 29,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 12,89</t>
+          <t>-12,68; 12,22</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,9</t>
+          <t>-10,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,36</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,97</t>
+          <t>-6,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -10,95</t>
+          <t>-25,22; -9,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 1,41</t>
+          <t>-13,3; 1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 0,39</t>
+          <t>-18,64; -2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,44; -9,49</t>
+          <t>-22,08; -9,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 8,71</t>
+          <t>-5,28; 8,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -0,05</t>
+          <t>-8,3; 5,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,02; -11,59</t>
+          <t>-22,28; -11,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,97</t>
+          <t>-7,58; 3,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,35; -4,42</t>
+          <t>-11,84; -0,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-12,17%</t>
+          <t>-16,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,24%</t>
+          <t>-4,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,24%</t>
+          <t>-12,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,7; -17,68</t>
+          <t>-37,29; -16,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 2,33</t>
+          <t>-18,95; 3,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 0,84</t>
+          <t>-28,43; -3,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,12; -29,77</t>
+          <t>-58,11; -30,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 28,24</t>
+          <t>-14,17; 27,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -0,3</t>
+          <t>-21,41; 17,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,45; -24,58</t>
+          <t>-43,11; -25,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 6,26</t>
+          <t>-14,56; 7,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,14; -8,99</t>
+          <t>-22,95; -2,08</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-25,19</t>
+          <t>-26,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-14,17</t>
+          <t>-13,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-19,93</t>
+          <t>-19,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 23,49</t>
+          <t>4,99; 24,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 8,02</t>
+          <t>-10,69; 8,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,98; -16,32</t>
+          <t>-33,63; -17,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 11,09</t>
+          <t>-4,57; 11,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,74</t>
+          <t>-8,52; 5,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -8,45</t>
+          <t>-20,43; -7,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 15,61</t>
+          <t>2,33; 15,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 5,53</t>
+          <t>-7,65; 4,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -14,59</t>
+          <t>-24,7; -14,75</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-59,11%</t>
+          <t>-61,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-77,5%</t>
+          <t>-73,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-66,03%</t>
+          <t>-65,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,88; 61,92</t>
+          <t>10,13; 66,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 21,11</t>
+          <t>-21,96; 21,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,32; -44,31</t>
+          <t>-70,66; -44,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 79,56</t>
+          <t>-21,74; 80,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 46,96</t>
+          <t>-37,63; 42,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,08; -58,48</t>
+          <t>-86,29; -53,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,31; 60,11</t>
+          <t>7,21; 58,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 20,78</t>
+          <t>-22,62; 18,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,5; -53,96</t>
+          <t>-74,04; -54,59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-9,48</t>
+          <t>-10,5</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-5,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 2,49</t>
+          <t>-13,67; 2,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 7,55</t>
+          <t>-7,45; 7,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -1,92</t>
+          <t>-17,71; -2,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -1,33</t>
+          <t>-17,54; -0,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 6,88</t>
+          <t>-8,98; 7,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 6,65</t>
+          <t>-8,89; 5,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -1,8</t>
+          <t>-13,46; -1,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 4,82</t>
+          <t>-7,14; 5,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 0,35</t>
+          <t>-10,83; 0,38</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-13,39%</t>
+          <t>-14,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-3,82%</t>
+          <t>-4,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-9,17%</t>
+          <t>-10,6%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 3,86</t>
+          <t>-18,85; 2,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 11,23</t>
+          <t>-9,79; 10,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -2,84</t>
+          <t>-23,97; -4,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,85; -3,92</t>
+          <t>-41,18; -2,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 19,19</t>
+          <t>-21,2; 19,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 19,67</t>
+          <t>-20,85; 15,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -3,43</t>
+          <t>-23,32; -2,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 9,29</t>
+          <t>-12,49; 9,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 0,68</t>
+          <t>-19,06; 0,56</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,72</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,26</t>
+          <t>7,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,63</t>
+          <t>6,12; 18,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,86; 18,01</t>
+          <t>6,82; 18,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 11,09</t>
+          <t>-1,81; 9,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,87; 12,32</t>
+          <t>2,82; 12,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,38; 21,76</t>
+          <t>11,99; 21,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,14; 53,81</t>
+          <t>6,65; 15,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,04</t>
+          <t>4,75; 12,85</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,59</t>
+          <t>10,62; 18,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,58; 35,36</t>
+          <t>3,57; 11,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>140,1%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,26; 42,18</t>
+          <t>12,7; 42,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>14,61; 43,62</t>
+          <t>14,24; 45,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 25,9</t>
+          <t>-4,01; 23,35</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,86; 70,36</t>
+          <t>12,36; 71,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>50,97; 122,47</t>
+          <t>53,51; 125,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,29; 301,82</t>
+          <t>28,94; 87,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,19; 43,09</t>
+          <t>13,81; 42,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31,6; 63,2</t>
+          <t>31,41; 62,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19,87; 112,27</t>
+          <t>10,06; 37,44</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-33,46</t>
+          <t>-23,96</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-13,11</t>
+          <t>-13,23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-21,75</t>
+          <t>-18,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -3,42</t>
+          <t>-13,5; -3,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -2,26</t>
+          <t>-12,7; -1,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-48,89; -20,48</t>
+          <t>-29,15; -18,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -0,08</t>
+          <t>-8,77; 0,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 7,62</t>
+          <t>-1,83; 7,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -9,04</t>
+          <t>-16,92; -9,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -3,32</t>
+          <t>-10,54; -3,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 1,45</t>
+          <t>-5,75; 1,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-31,84; -16,58</t>
+          <t>-21,75; -15,0</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-52,82%</t>
+          <t>-37,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-48,36%</t>
+          <t>-48,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-48,62%</t>
+          <t>-40,99%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,89; -5,67</t>
+          <t>-20,46; -4,83</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,2; -3,59</t>
+          <t>-19,39; -3,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-78,29; -33,09</t>
+          <t>-44,56; -30,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -0,16</t>
+          <t>-29,42; 1,57</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 31,43</t>
+          <t>-6,29; 28,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-57,84; -36,33</t>
+          <t>-57,99; -37,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -7,74</t>
+          <t>-22,55; -7,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 3,43</t>
+          <t>-12,47; 2,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-71,13; -37,38</t>
+          <t>-46,57; -34,0</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-9,18</t>
+          <t>-7,21</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,68</t>
+          <t>-1,62; 3,62</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,6</t>
+          <t>-0,44; 4,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -4,75</t>
+          <t>-10,0; -4,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,2</t>
+          <t>-1,1; 3,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,4</t>
+          <t>3,84; 8,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 16,54</t>
+          <t>-2,2; 1,87</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,77</t>
+          <t>-0,83; 2,59</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,71</t>
+          <t>2,39; 5,88</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,24</t>
+          <t>-5,42; -1,96</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-16,7%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-9,42%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,85</t>
+          <t>-2,8; 6,76</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,57</t>
+          <t>-0,76; 8,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,37; -8,77</t>
+          <t>-17,8; -8,74</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 13,41</t>
+          <t>-4,23; 13,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>16,05; 35,4</t>
+          <t>14,98; 35,18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 66,32</t>
+          <t>-8,6; 8,25</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,22</t>
+          <t>-2,1; 6,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>5,77; 14,83</t>
+          <t>5,89; 15,22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 8,3</t>
+          <t>-13,38; -5,08</t>
         </is>
       </c>
     </row>
